--- a/PMS-struts/src/com/dp/plat/template/spotCheck.xlsx
+++ b/PMS-struts/src/com/dp/plat/template/spotCheck.xlsx
@@ -1,62 +1,69 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="90" windowWidth="13875" windowHeight="10215"/>
+    <workbookView windowWidth="24000" windowHeight="9840"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="现场验货单" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
+    <t xml:space="preserve"> 现场验货单</t>
+  </si>
+  <si>
+    <t>项目名称</t>
+  </si>
+  <si>
+    <t>此处填写项目名称</t>
+  </si>
+  <si>
+    <t>合同号</t>
+  </si>
+  <si>
+    <t>此处填写项目合同号</t>
+  </si>
+  <si>
+    <t>产品编码</t>
+  </si>
+  <si>
+    <t>产品型号</t>
+  </si>
+  <si>
     <t>数量</t>
   </si>
   <si>
-    <t xml:space="preserve"> 现场验货单</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>序列号</t>
   </si>
   <si>
-    <t>项目名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>合同号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>序列号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品编码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品型号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>备注</t>
   </si>
   <si>
     <t>经核对，现场到货设备与上述清单设备一致，准确无误。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">验货人签字：            </t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">      </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>年</t>
@@ -65,7 +72,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">         </t>
     </r>
@@ -73,7 +80,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>月</t>
@@ -82,7 +88,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">         </t>
     </r>
@@ -90,7 +96,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>日</t>
@@ -99,108 +104,56 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">        </t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">验货人签字：            </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>此处填写项目名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>此处填写项目合同号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="16">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="30">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <b/>
+      <sz val="20"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="10"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -208,37 +161,371 @@
       <sz val="9"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -247,30 +534,110 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -278,133 +645,317 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -695,17 +1246,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.875" customWidth="1"/>
-    <col min="2" max="2" width="10.125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="10.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="25.375" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
     <col min="5" max="5" width="61" customWidth="1"/>
@@ -713,157 +1264,133 @@
     <col min="7" max="7" width="6.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.5">
-      <c r="A1" s="30" t="s">
+    <row r="1" ht="25.5" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" spans="1:7">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="25"/>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="29" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="33" t="s">
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" ht="27.75" customHeight="1" spans="1:7">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="13"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="13"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="24"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="18"/>
     </row>
-    <row r="4" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A4" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="32" t="s">
+    <row r="10" spans="1:7">
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="21"/>
+      <c r="E10" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="23"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="23"/>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="31"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="21" t="s">
+    <row r="11" ht="15" spans="1:7">
+      <c r="A11" s="19"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="24"/>
+      <c r="E11" s="25" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="7"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="9"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="5"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="3"/>
-      <c r="E10" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="16"/>
-    </row>
-    <row r="11" spans="1:7" ht="15">
-      <c r="A11" s="2"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="4"/>
-      <c r="E11" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:F4"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageMargins left="0.748031496062992" right="0.748031496062992" top="0.984251968503937" bottom="0.984251968503937" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200"/>
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;L&amp;9现场验货单附件</oddHeader>
     <oddFooter>&amp;L&amp;9数据导出时间：&amp;R&amp;9&amp;P/&amp;N</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
 </file>